--- a/TAPPs for review/EPMA_TAPP_v88_Review_Workbook_EDS_Point_Analysis.xlsx
+++ b/TAPPs for review/EPMA_TAPP_v88_Review_Workbook_EDS_Point_Analysis.xlsx
@@ -1502,7 +1502,7 @@
           <t>EML-EPMA-CC v2, EPMA-WDS+EDS major and minor elements in carbonaceous-chondrite silicates, oxides, sulfides, phosphates and carbonates</t>
         </is>
       </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1522,7 +1522,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J3" s="27" t="inlineStr">
+      <c r="J3" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -1570,7 +1570,7 @@
           <t>EPMA-WDS+EDS (combines wavelength-dispersive and energy-dispersive spectrometry)</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1590,7 +1590,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J4" s="27" t="inlineStr">
+      <c r="J4" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -1638,7 +1638,7 @@
           <t>Example Microanalysis Laboratory</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1658,7 +1658,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -1706,7 +1706,7 @@
           <t>Example Microanalysis Laboratory</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1726,7 +1726,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="J6" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -1774,7 +1774,7 @@
           <t>https://ror.org/0example00</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1794,7 +1794,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="J7" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -1842,7 +1842,7 @@
           <t>January 2025</t>
         </is>
       </c>
-      <c r="F8" s="27" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1862,7 +1862,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="J8" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -1910,7 +1910,7 @@
           <t>Example Agency award EX-INST-0001 (instrument); award EX-DEV-0002 (procedure development)</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1930,7 +1930,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="J9" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -1978,7 +1978,7 @@
           <t>Example et al. (2025), doi:10.0000/example.2025.001</t>
         </is>
       </c>
-      <c r="F10" s="27" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -1998,7 +1998,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="J10" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2046,7 +2046,7 @@
           <t>doi:10.0000/example.epma-cc.v2</t>
         </is>
       </c>
-      <c r="F11" s="27" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2066,7 +2066,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2114,7 +2114,7 @@
           <t>EML-2026-0412-A</t>
         </is>
       </c>
-      <c r="F12" s="27" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2134,7 +2134,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="J12" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2182,7 +2182,7 @@
           <t>Analyst A (ORCID 0000-0000-0000-0000)</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2202,7 +2202,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="J13" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2250,7 +2250,7 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="F14" s="27" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2270,7 +2270,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="J14" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2318,7 +2318,7 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="F15" s="27" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2338,7 +2338,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="J15" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2386,7 +2386,7 @@
           <t>Example Agency award EX-SCI-0003</t>
         </is>
       </c>
-      <c r="F16" s="27" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2406,7 +2406,7 @@
           <t>— Set by registration requirements; no review needed</t>
         </is>
       </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2450,7 +2450,7 @@
           <t>SEM; NanoSIMS (oxygen isotopes of carbonates, Example Isotope Laboratory)</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the procedure.</t>
         </is>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="I17" s="37" t="n"/>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="J17" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the session.</t>
         </is>
@@ -2498,7 +2498,7 @@
           <t>EPMA carbonate compositions select the matrix-matched reference material for the NanoSIMS mass-fractionation correction; SEM first, EPMA next (non-destructive), NanoSIMS last (sputtering destroys the analysed volume)</t>
         </is>
       </c>
-      <c r="F18" s="27" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I18" s="37" t="n"/>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="J18" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2546,7 +2546,7 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="I19" s="37" t="n"/>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="J19" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2594,7 +2594,7 @@
           <t>same submission</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="F20" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="I20" s="37" t="n"/>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="J20" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the session.</t>
         </is>
@@ -2666,7 +2666,7 @@
           <t>Silicate mineral (olivine, pyroxene); oxide (magnetite, chromite, ilmenite); sulfide (pyrrhotite, pentlandite); phosphate (apatite, merrillite); carbonate (calcite, dolomite, breunnerite), in carbonaceous-chondrite material</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F23" s="30" t="inlineStr">
         <is>
           <t>List the material types the procedure is designed to analyse.</t>
         </is>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="I23" s="37" t="n"/>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="J23" s="30" t="inlineStr">
         <is>
           <t>List the material types the procedure is designed to analyse.</t>
         </is>
@@ -2714,7 +2714,7 @@
           <t>Epoxy mount, dry-polished with diamond to 0.25 µm, carbon coated to 20 nm, for EX-CC-01; the same, plus Ar-ion polishing after the final diamond step, for EX-CC-02</t>
         </is>
       </c>
-      <c r="F24" s="27" t="inlineStr">
+      <c r="F24" s="30" t="inlineStr">
         <is>
           <t>Give one value; each "Sample Name" entry in a session inherits it.</t>
         </is>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="I24" s="37" t="n"/>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="J24" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Sample Name".</t>
         </is>
@@ -2762,7 +2762,7 @@
           <t>EX-CC-01; EX-CC-02</t>
         </is>
       </c>
-      <c r="F25" s="27" t="inlineStr">
+      <c r="F25" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="I25" s="37" t="n"/>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="J25" s="30" t="inlineStr">
         <is>
           <t>List every sample analysed in the session.</t>
         </is>
@@ -2810,7 +2810,7 @@
           <t>Analysis point (one point analysis = one result), labelled by particle and point number</t>
         </is>
       </c>
-      <c r="F26" s="27" t="inlineStr">
+      <c r="F26" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="I26" s="37" t="n"/>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="J26" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -2858,7 +2858,7 @@
           <t>P1-01–P1-12, P2-01–P2-11, P3-01–P3-06 for EX-CC-01 (29 points); P1-01–P1-16, P2-01–P2-08 for EX-CC-02 (24 points)</t>
         </is>
       </c>
-      <c r="F27" s="27" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="I27" s="37" t="n"/>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="J27" s="30" t="inlineStr">
         <is>
           <t>For each "Sample Name", list the analysis points analysed in it.</t>
         </is>
@@ -2906,7 +2906,7 @@
           <t>Silicate mineral for P1-01–P1-12, oxide for P2-01–P2-06, sulfide for P2-07–P2-11, phosphate for P3-01–P3-06 (EX-CC-01); carbonate for P1-01–P1-16, silicate mineral for P2-01–P2-08 (EX-CC-02)</t>
         </is>
       </c>
-      <c r="F28" s="27" t="inlineStr">
+      <c r="F28" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="I28" s="37" t="n"/>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="J28" s="30" t="inlineStr">
         <is>
           <t>For each "Sample Name", give one value for each of its "Sampling Unit Name" entries.</t>
         </is>
@@ -2954,7 +2954,7 @@
           <t>IGSN:EXAMPLE0001 for EX-CC-01; IGSN:EXAMPLE0002 for EX-CC-02</t>
         </is>
       </c>
-      <c r="F29" s="27" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I29" s="37" t="n"/>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="J29" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Sample Name".</t>
         </is>
@@ -3002,7 +3002,7 @@
           <t>Grains at least 5 µm across (10 µm for phosphates and carbonates); at least 3 µm from boundaries, cracks and inclusions in BSE (5 µm for defocused or rastered beams); phase confirmed from its EDS spectrum first</t>
         </is>
       </c>
-      <c r="F30" s="27" t="inlineStr">
+      <c r="F30" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="I30" s="37" t="n"/>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="J30" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -3050,7 +3050,7 @@
           <t>BSE imaging and EDS maps (Mg, Si, Fe, Ca, S, P) on a field-emission SEM at 15 kV and 1 nA, registered to stage coordinates, each point labelled on its particle's BSE image — for both EX-CC-01 and EX-CC-02</t>
         </is>
       </c>
-      <c r="F31" s="27" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>Give one value; each "Sample Name" entry in a session inherits it.</t>
         </is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="I31" s="37" t="n"/>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="J31" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Sample Name".</t>
         </is>
@@ -3122,7 +3122,7 @@
           <t>JEOL</t>
         </is>
       </c>
-      <c r="F34" s="27" t="inlineStr">
+      <c r="F34" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="I34" s="37" t="n"/>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="J34" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -3170,7 +3170,7 @@
           <t>JXA-8530F Plus</t>
         </is>
       </c>
-      <c r="F35" s="27" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the procedure.</t>
         </is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="I35" s="37" t="n"/>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="J35" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the session.</t>
         </is>
@@ -3218,7 +3218,7 @@
           <t>Schottky field-emission</t>
         </is>
       </c>
-      <c r="F36" s="27" t="inlineStr">
+      <c r="F36" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="I36" s="37" t="n"/>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="J36" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -3266,7 +3266,7 @@
           <t>Probe for EPMA v13 (Probe Software)</t>
         </is>
       </c>
-      <c r="F37" s="27" t="inlineStr">
+      <c r="F37" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I37" s="37" t="n"/>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="J37" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -3314,7 +3314,7 @@
           <t>Probe for EPMA v13</t>
         </is>
       </c>
-      <c r="F38" s="27" t="inlineStr">
+      <c r="F38" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the procedure.</t>
         </is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="I38" s="37" t="n"/>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="J38" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the session.</t>
         </is>
@@ -3362,7 +3362,7 @@
           <t>Integrated silicon drift detector: 30 mm² active area, ultra-thin polymer window, 40° take-off angle</t>
         </is>
       </c>
-      <c r="F39" s="27" t="inlineStr">
+      <c r="F39" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the procedure.</t>
         </is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="I39" s="37" t="n"/>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="J39" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the session.</t>
         </is>
@@ -3434,7 +3434,7 @@
           <t>EDS point analysis; EDS mapping; WDS point analysis; WDS mapping</t>
         </is>
       </c>
-      <c r="F42" s="27" t="inlineStr">
+      <c r="F42" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the procedure.</t>
         </is>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="I42" s="37" t="n"/>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="J42" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the session.</t>
         </is>
@@ -3482,7 +3482,7 @@
           <t>Focused for silicate minerals, oxides and sulfides; defocused for phosphates; rastered for carbonates</t>
         </is>
       </c>
-      <c r="F43" s="27" t="inlineStr">
+      <c r="F43" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="I43" s="37" t="n"/>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="J43" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3530,7 +3530,7 @@
           <t>15 kV (the laboratory's standard operating voltage)</t>
         </is>
       </c>
-      <c r="F44" s="27" t="inlineStr">
+      <c r="F44" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I44" s="37" t="n"/>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="J44" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -3578,7 +3578,7 @@
           <t>20 nA for silicate minerals, oxides and sulfides; 8 nA for phosphates; 4 nA for carbonates</t>
         </is>
       </c>
-      <c r="F45" s="27" t="inlineStr">
+      <c r="F45" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="I45" s="37" t="n"/>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="J45" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3626,7 +3626,7 @@
           <t>1 µm (focused) for silicate minerals, oxides and sulfides; 5 µm (defocused) for phosphates; focused within the raster for carbonates</t>
         </is>
       </c>
-      <c r="F46" s="27" t="inlineStr">
+      <c r="F46" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I46" s="37" t="n"/>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="J46" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3674,7 +3674,7 @@
           <t>5 × 5 µm for carbonates</t>
         </is>
       </c>
-      <c r="F47" s="27" t="inlineStr">
+      <c r="F47" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="I47" s="37" t="n"/>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="J47" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3722,7 +3722,7 @@
           <t>Defocused beam for phosphates; rastered beam for carbonates</t>
         </is>
       </c>
-      <c r="F48" s="27" t="inlineStr">
+      <c r="F48" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="I48" s="37" t="n"/>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="J48" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Material".</t>
         </is>
@@ -3770,7 +3770,7 @@
           <t>Beam current measured with the Faraday cup before each point and at the start of each map line, intensities normalised to it; primary standards re-measured at the start and end of the session, drift interpolated linearly with time</t>
         </is>
       </c>
-      <c r="F49" s="27" t="inlineStr">
+      <c r="F49" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="I49" s="37" t="n"/>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="J49" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -3818,7 +3818,7 @@
           <t>Si, Ti, Al, Cr, Fe, Mn, Mg, Ca, Na, K, P, S, F, Cl, Ni, Co, O, C (18 elements)</t>
         </is>
       </c>
-      <c r="F50" s="27" t="inlineStr">
+      <c r="F50" s="30" t="inlineStr">
         <is>
           <t>List the elements the procedure determines.</t>
         </is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="I50" s="37" t="n"/>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="J50" s="30" t="inlineStr">
         <is>
           <t>List the elements the procedure determines.</t>
         </is>
@@ -3866,7 +3866,7 @@
           <t>Si, Mg, Fe, Ca, S</t>
         </is>
       </c>
-      <c r="F51" s="27" t="inlineStr">
+      <c r="F51" s="30" t="inlineStr">
         <is>
           <t>List each monitored element, grouped under the "Target Species" it serves (some serve none).</t>
         </is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="I51" s="37" t="n"/>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="J51" s="30" t="inlineStr">
         <is>
           <t>List each monitored element, grouped under the "Target Species" it serves (some serve none).</t>
         </is>
@@ -3914,7 +3914,7 @@
           <t>SiO₂, TiO₂, Al₂O₃, Cr₂O₃, FeO (total Fe), MnO, MgO, CaO, Na₂O, K₂O, P₂O₅, NiO, CoO in wt%; S, F, Cl in wt%; O equivalent of F and Cl; CO₂ by stoichiometry (carbonates); totals; structural formulas in apfu</t>
         </is>
       </c>
-      <c r="F52" s="27" t="inlineStr">
+      <c r="F52" s="30" t="inlineStr">
         <is>
           <t>List every quantity reported, with its unit.</t>
         </is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="I52" s="37" t="n"/>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="J52" s="30" t="inlineStr">
         <is>
           <t>List every quantity reported, with its unit.</t>
         </is>
@@ -3962,7 +3962,7 @@
           <t>EDS for Si, Mg, Fe, Ca, S</t>
         </is>
       </c>
-      <c r="F53" s="27" t="inlineStr">
+      <c r="F53" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Monitored Element".</t>
         </is>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="I53" s="37" t="n"/>
-      <c r="J53" s="27" t="inlineStr">
+      <c r="J53" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Monitored Element".</t>
         </is>
@@ -4010,7 +4010,7 @@
           <t>Kα for Si, Mg, Fe, Ca, S</t>
         </is>
       </c>
-      <c r="F54" s="27" t="inlineStr">
+      <c r="F54" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Monitored Element".</t>
         </is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="I54" s="37" t="n"/>
-      <c r="J54" s="27" t="inlineStr">
+      <c r="J54" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Monitored Element".</t>
         </is>
@@ -4058,7 +4058,7 @@
           <t>30 s per point</t>
         </is>
       </c>
-      <c r="F55" s="27" t="inlineStr">
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="I55" s="37" t="n"/>
-      <c r="J55" s="27" t="inlineStr">
+      <c r="J55" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -4106,7 +4106,7 @@
           <t>Point spectra; spectrum images (full spectrum at every pixel); no line scans</t>
         </is>
       </c>
-      <c r="F56" s="27" t="inlineStr">
+      <c r="F56" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the procedure.</t>
         </is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="I56" s="37" t="n"/>
-      <c r="J56" s="27" t="inlineStr">
+      <c r="J56" s="30" t="inlineStr">
         <is>
           <t>Give one or more values for the session.</t>
         </is>
@@ -4178,7 +4178,7 @@
           <t>Armstrong/Love–Scott φ(ρz) matrix correction (Armstrong 1995) in Probe for EPMA</t>
         </is>
       </c>
-      <c r="F59" s="27" t="inlineStr">
+      <c r="F59" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="I59" s="37" t="n"/>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="J59" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -4226,7 +4226,7 @@
           <t>FFAST (Chantler et al. 2005)</t>
         </is>
       </c>
-      <c r="F60" s="27" t="inlineStr">
+      <c r="F60" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I60" s="37" t="n"/>
-      <c r="J60" s="27" t="inlineStr">
+      <c r="J60" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -4274,7 +4274,7 @@
           <t>Removed by filter fitting for Si, Mg, Fe, Ca, S</t>
         </is>
       </c>
-      <c r="F61" s="27" t="inlineStr">
+      <c r="F61" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Monitored Element".</t>
         </is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="I61" s="37" t="n"/>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="J61" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Monitored Element".</t>
         </is>
@@ -4322,7 +4322,7 @@
           <t>Linear for Na; exponential for F (in apatite); none for other elements</t>
         </is>
       </c>
-      <c r="F62" s="27" t="inlineStr">
+      <c r="F62" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="I62" s="37" t="n"/>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="J62" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -4370,7 +4370,7 @@
           <t>Directly from measured intensities for every measured element; by stoichiometry from cation valences for O; as CO₂ by stoichiometry for C (carbonates only); OH in apatite by difference, F + Cl + OH = 1 apfu (Ketcham 2015)</t>
         </is>
       </c>
-      <c r="F63" s="27" t="inlineStr">
+      <c r="F63" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="I63" s="37" t="n"/>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="J63" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -4418,7 +4418,7 @@
           <t>Oxygen equivalent of F and Cl subtracted from the total (apatite)</t>
         </is>
       </c>
-      <c r="F64" s="27" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="I64" s="37" t="n"/>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -4466,7 +4466,7 @@
           <t>Filter fitting: a top-hat filter followed by least-squares fitting to measured standard spectra</t>
         </is>
       </c>
-      <c r="F65" s="27" t="inlineStr">
+      <c r="F65" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="I65" s="37" t="n"/>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="J65" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -4514,7 +4514,7 @@
           <t>Apparent concentration measured on Ni- and Co-free synthetic forsterite subtracted, for Ni and Co; none for other elements</t>
         </is>
       </c>
-      <c r="F66" s="27" t="inlineStr">
+      <c r="F66" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="I66" s="37" t="n"/>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="J66" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -4562,7 +4562,7 @@
           <t>Structural formulas normalised to a fixed anion basis: 4 O for olivine and spinels, 6 O for pyroxene and dolomite, 3 O for calcite, 13 anions for apatite (Ketcham 2015); none for other reported variables</t>
         </is>
       </c>
-      <c r="F67" s="27" t="inlineStr">
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I67" s="37" t="n"/>
-      <c r="J67" s="27" t="inlineStr">
+      <c r="J67" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -4610,7 +4610,7 @@
           <t>None, for every reported variable (concentrations from k-ratios against the primary standards)</t>
         </is>
       </c>
-      <c r="F68" s="27" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="I68" s="37" t="n"/>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -4658,7 +4658,7 @@
           <t>35 ± 9 µg/g for Ni; 22 ± 8 µg/g for Co (n = 5)</t>
         </is>
       </c>
-      <c r="F69" s="27" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I69" s="37" t="n"/>
-      <c r="J69" s="27" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -4706,7 +4706,7 @@
           <t>Rules: totals 98.5–101.5 wt% (silicates, oxides, sulfides), 96.0–101.5 (apatite), 98.0–102.0 (carbonates); cation sum within ±0.03 apfu; no overlap with a second phase; beam drift under 1%. Outcome: 53 points acquired, 45 included; excluded P3-02 and P3-05 from apatite in EX-CC-01 and P1-03, P1-07 from dolomite in EX-CC-02 (totals), P2-07 and P2-09 from pyrrhotite in EX-CC-01 and P1-16 from calcite in EX-CC-02 (overlap), P2-05 from olivine in EX-CC-02 (drift)</t>
         </is>
       </c>
-      <c r="F70" s="27" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>Give one value; each "Combined Result" entry in a session inherits it.</t>
         </is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="I70" s="37" t="n"/>
-      <c r="J70" s="27" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Combined Result".</t>
         </is>
@@ -4754,7 +4754,7 @@
           <t>Arithmetic mean of the included points, per phase within each sample, for every oxide and element concentration; maps and structural formulas not combined</t>
         </is>
       </c>
-      <c r="F71" s="27" t="inlineStr">
+      <c r="F71" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I71" s="37" t="n"/>
-      <c r="J71" s="27" t="inlineStr">
+      <c r="J71" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -4802,7 +4802,7 @@
           <t>Olivine in EX-CC-01 (P1-01–P1-08); pyroxene in EX-CC-01 (P1-09–P1-12); magnetite in EX-CC-01 (P2-01–P2-06); pyrrhotite in EX-CC-01 (P2-07–P2-11); apatite in EX-CC-01 (P3-01–P3-06); dolomite in EX-CC-02 (P1-01–P1-10); calcite in EX-CC-02 (P1-11–P1-16); olivine in EX-CC-02 (P2-01–P2-08)</t>
         </is>
       </c>
-      <c r="F72" s="27" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I72" s="37" t="n"/>
-      <c r="J72" s="27" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>List every reported value that combines several individual results, saying what each combines.</t>
         </is>
@@ -4850,7 +4850,7 @@
           <t>IUPAC 2021 standard atomic weights (Prohaska et al. 2022)</t>
         </is>
       </c>
-      <c r="F73" s="27" t="inlineStr">
+      <c r="F73" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="I73" s="37" t="n"/>
-      <c r="J73" s="27" t="inlineStr">
+      <c r="J73" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -4922,7 +4922,7 @@
           <t>Springwater olivine USNM 2566 for Si, Mg; Rockport fayalite USNM 85276 for Fe; diopside USNM 117733 for Ca; dolomite USNM 10057 for Ca, Mg in carbonates; synthetic FeS for S (Smithsonian values: Jarosewich et al. 1980)</t>
         </is>
       </c>
-      <c r="F76" s="27" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>For each "Target Material", give one value for each "Target Species".</t>
         </is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="I76" s="37" t="n"/>
-      <c r="J76" s="27" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>For each "Target Material", give one value for each "Target Species".</t>
         </is>
@@ -4970,7 +4970,7 @@
           <t>San Carlos olivine USNM 111312/444; Kakanui augite USNM 122142; Durango apatite USNM 104021; chromite USNM 117075; calcite USNM 136321 (accepted values: Jarosewich et al. 1980)</t>
         </is>
       </c>
-      <c r="F77" s="27" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>List the secondary reference materials run as unknowns.</t>
         </is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="I77" s="37" t="n"/>
-      <c r="J77" s="27" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>List the secondary reference materials run as unknowns.</t>
         </is>
@@ -5018,7 +5018,7 @@
           <t>No for Si, Mg, Fe, Ca, S</t>
         </is>
       </c>
-      <c r="F78" s="27" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="I78" s="37" t="n"/>
-      <c r="J78" s="27" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -5066,7 +5066,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F79" s="27" t="inlineStr">
+      <c r="F79" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I79" s="37" t="n"/>
-      <c r="J79" s="27" t="inlineStr">
+      <c r="J79" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -5114,7 +5114,7 @@
           <t>None required</t>
         </is>
       </c>
-      <c r="F80" s="27" t="inlineStr">
+      <c r="F80" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="I80" s="37" t="n"/>
-      <c r="J80" s="27" t="inlineStr">
+      <c r="J80" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Target Species".</t>
         </is>
@@ -5162,7 +5162,7 @@
           <t>0.11 wt% for SiO₂; 0.09 for MgO; 0.14 for FeO; 0.10 for CaO; 0.08 for S</t>
         </is>
       </c>
-      <c r="F81" s="27" t="inlineStr">
+      <c r="F81" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="I81" s="37" t="n"/>
-      <c r="J81" s="27" t="inlineStr">
+      <c r="J81" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -5210,7 +5210,7 @@
           <t>3σ of the background counts, for every reported variable</t>
         </is>
       </c>
-      <c r="F82" s="27" t="inlineStr">
+      <c r="F82" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="I82" s="37" t="n"/>
-      <c r="J82" s="27" t="inlineStr">
+      <c r="J82" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -5258,7 +5258,7 @@
           <t>0.4–0.7% for oxides above 10 wt%; 0.9–1.6% for FeO and Al₂O₃; 2–4% for TiO₂, Na₂O, F and Cl; 4% for NiO in San Carlos olivine (1σ RSD; San Carlos olivine n = 9, Kakanui augite n = 6, Durango apatite n = 6, chromite n = 5, calcite n = 6)</t>
         </is>
       </c>
-      <c r="F83" s="27" t="inlineStr">
+      <c r="F83" s="30" t="inlineStr">
         <is>
           <t>For each "Secondary Reference Material", give one value for each "Reported Variable".</t>
         </is>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="I83" s="37" t="n"/>
-      <c r="J83" s="27" t="inlineStr">
+      <c r="J83" s="30" t="inlineStr">
         <is>
           <t>For each "Secondary Reference Material", give one value for each "Reported Variable".</t>
         </is>
@@ -5306,7 +5306,7 @@
           <t>Within ±1.2% relative for all major oxides; within ±2.6% for minor oxides and halogens</t>
         </is>
       </c>
-      <c r="F84" s="27" t="inlineStr">
+      <c r="F84" s="30" t="inlineStr">
         <is>
           <t>For each "Secondary Reference Material", give one value for each "Reported Variable".</t>
         </is>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="I84" s="37" t="n"/>
-      <c r="J84" s="27" t="inlineStr">
+      <c r="J84" s="30" t="inlineStr">
         <is>
           <t>For each "Secondary Reference Material", give one value for each "Reported Variable".</t>
         </is>
@@ -5354,7 +5354,7 @@
           <t>1σ from counting statistics on the peak and background, for every analysis and every reported variable; about 0.5% relative for SiO₂ and MgO in olivine</t>
         </is>
       </c>
-      <c r="F85" s="27" t="inlineStr">
+      <c r="F85" s="30" t="inlineStr">
         <is>
           <t>Give one value for each "Reported Variable".</t>
         </is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I85" s="37" t="n"/>
-      <c r="J85" s="27" t="inlineStr">
+      <c r="J85" s="30" t="inlineStr">
         <is>
           <t>For each "Sample Name", give one value for every "Reported Variable" at every "Sampling Unit Name" entry.</t>
         </is>
@@ -5402,7 +5402,7 @@
           <t>18–26%</t>
         </is>
       </c>
-      <c r="F86" s="27" t="inlineStr">
+      <c r="F86" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="I86" s="37" t="n"/>
-      <c r="J86" s="27" t="inlineStr">
+      <c r="J86" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
@@ -5450,7 +5450,7 @@
           <t>MSWD of the included points about the mean: for olivine in EX-CC-01, 0.9 for NiO to 2.3 for CaO, and 4.6 for FeO (Fe–Mg zoning); likewise for every other combined result</t>
         </is>
       </c>
-      <c r="F87" s="27" t="inlineStr">
+      <c r="F87" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="I87" s="37" t="n"/>
-      <c r="J87" s="27" t="inlineStr">
+      <c r="J87" s="30" t="inlineStr">
         <is>
           <t>For each "Combined Result", give one value for each "Reported Variable".</t>
         </is>
@@ -5498,7 +5498,7 @@
           <t>Standard error of the mean (1 s.d./√n): for olivine in EX-CC-01, 0.08 wt% for SiO₂, 0.12 for MgO, 0.04 for FeO; likewise for every other combined result</t>
         </is>
       </c>
-      <c r="F88" s="27" t="inlineStr">
+      <c r="F88" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="I88" s="37" t="n"/>
-      <c r="J88" s="27" t="inlineStr">
+      <c r="J88" s="30" t="inlineStr">
         <is>
           <t>For each "Combined Result", give one value for each "Reported Variable".</t>
         </is>
@@ -5546,7 +5546,7 @@
           <t>Particle P2 of EX-CC-02 partly plucked during ion polishing; its analyses lie on the remaining fragment. No other anomalies, instrument modifications or departures</t>
         </is>
       </c>
-      <c r="F89" s="27" t="inlineStr">
+      <c r="F89" s="30" t="inlineStr">
         <is>
           <t>Give one value for the procedure.</t>
         </is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I89" s="37" t="n"/>
-      <c r="J89" s="27" t="inlineStr">
+      <c r="J89" s="30" t="inlineStr">
         <is>
           <t>Give one value for the session.</t>
         </is>
